--- a/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
+++ b/results/ate_iptw_cox_standard_IPTW_Cox_Standard_retention.xlsx
@@ -582,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.006</v>
+        <v>0.054</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004</v>
+        <v>0.039</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.075</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.054</v>
+        <v>0.027</v>
       </c>
       <c r="D8" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003</v>
+        <v>-0.018</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.014</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.027</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008</v>
+        <v>-0.028</v>
       </c>
       <c r="E10" t="n">
-        <v>0.019</v>
+        <v>0.04100000000000001</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -744,7 +744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0.013</v>
       </c>
       <c r="D12" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.014</v>
+        <v>0</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.039</v>
+        <v>0.186</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E13" t="n">
-        <v>0.015</v>
+        <v>0.163</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.152</v>
+        <v>0.003</v>
       </c>
       <c r="D14" t="n">
-        <v>0.023</v>
+        <v>-0.013</v>
       </c>
       <c r="E14" t="n">
-        <v>0.129</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.061</v>
+        <v>-0.081</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.004</v>
+        <v>-0.031</v>
       </c>
       <c r="E15" t="n">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003999999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.018</v>
+        <v>0.028</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.028</v>
+        <v>0.005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04100000000000001</v>
+        <v>0.003999999999999999</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.186</v>
+        <v>0.061</v>
       </c>
       <c r="D21" t="n">
-        <v>0.023</v>
+        <v>-0.004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.163</v>
+        <v>0.057</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1014,7 +1014,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.22</v>
+        <v>0.081</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.068</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>0.152</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.075</v>
+        <v>0.039</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.004</v>
+        <v>0.024</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.028</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="E26" t="n">
-        <v>0.022</v>
+        <v>-0.024</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,16 +1158,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.081</v>
+        <v>-0.152</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.402</v>
+        <v>-0.22</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.042</v>
+        <v>-0.068</v>
       </c>
       <c r="E29" t="n">
-        <v>0.36</v>
+        <v>0.152</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.024</v>
+        <v>0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.024</v>
+        <v>0.004</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="D31" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.081</v>
+        <v>-0.402</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.031</v>
+        <v>-0.042</v>
       </c>
       <c r="E32" t="n">
-        <v>0.05</v>
+        <v>0.36</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1373,7 +1373,7 @@
         <v>0.1488435642969905</v>
       </c>
       <c r="E2" t="n">
-        <v>1.761326673294262</v>
+        <v>1.761326673294263</v>
       </c>
       <c r="F2" t="n">
         <v>1.137318832200253</v>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.565853031636364</v>
+        <v>-2.565853031636363</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4408682502540031</v>
+        <v>0.4408682502540153</v>
       </c>
       <c r="D2" t="n">
-        <v>5.88477750371024e-09</v>
+        <v>5.884777503716e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02444271798652567</v>
+        <v>0.02444271798652564</v>
       </c>
       <c r="C3" t="n">
         <v>0.1018579889442992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8103546067770723</v>
+        <v>0.8103546067770725</v>
       </c>
     </row>
     <row r="4">
@@ -1628,10 +1628,10 @@
         <v>0.2756487250199114</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2218639632557894</v>
+        <v>0.2218639632557896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2140808095272575</v>
+        <v>0.2140808095272582</v>
       </c>
     </row>
     <row r="5">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7869972837033653</v>
+        <v>0.7869972837033652</v>
       </c>
       <c r="C5" t="n">
         <v>0.1664421345423985</v>
@@ -1660,10 +1660,10 @@
         <v>-0.1791283976706459</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2049919256074305</v>
+        <v>0.2049919256074304</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3822100343131284</v>
+        <v>0.3822100343131282</v>
       </c>
     </row>
     <row r="7">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1904728809612528</v>
+        <v>0.1904728809612526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1830828687785755</v>
+        <v>0.1830828687785756</v>
       </c>
       <c r="D7" t="n">
-        <v>0.298170680257699</v>
+        <v>0.2981706802576993</v>
       </c>
     </row>
     <row r="8">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0258571496674143</v>
+        <v>0.02585714966741419</v>
       </c>
       <c r="C8" t="n">
         <v>0.1931377319540171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8934979973795411</v>
+        <v>0.8934979973795415</v>
       </c>
     </row>
     <row r="9">
@@ -1708,10 +1708,10 @@
         <v>1.078492441903574</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1625051351014595</v>
+        <v>0.1625051351014596</v>
       </c>
       <c r="D9" t="n">
-        <v>3.208557236657033e-11</v>
+        <v>3.208557236657092e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1453095305392678</v>
+        <v>0.145309530539267</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2667530368267064</v>
+        <v>0.2667530368267059</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5859362662578784</v>
+        <v>0.5859362662578798</v>
       </c>
     </row>
     <row r="11">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2258952284551363</v>
+        <v>0.2258952284551358</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2567372932128586</v>
+        <v>0.256737293212858</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3789301892340627</v>
+        <v>0.3789301892340629</v>
       </c>
     </row>
     <row r="12">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2238722198593792</v>
+        <v>-0.2238722198593797</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2921431009265689</v>
+        <v>0.2921431009265686</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4434917877305503</v>
+        <v>0.4434917877305491</v>
       </c>
     </row>
     <row r="13">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2014123494531396</v>
+        <v>0.201412349453139</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2595890034850308</v>
+        <v>0.2595890034850307</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4378143071063244</v>
+        <v>0.4378143071063257</v>
       </c>
     </row>
     <row r="14">
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2380082564065346</v>
+        <v>0.238008256406534</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2619585733909509</v>
+        <v>0.2619585733909519</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3635760286774802</v>
+        <v>0.3635760286774831</v>
       </c>
     </row>
     <row r="15">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2909332948528223</v>
+        <v>0.2909332948528215</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2546715666353526</v>
+        <v>0.2546715666353518</v>
       </c>
       <c r="D15" t="n">
         <v>0.2532935059734769</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1481947915129311</v>
+        <v>0.1481947915129307</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2510856640294903</v>
+        <v>0.2510856640294911</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5550458059667072</v>
+        <v>0.5550458059667095</v>
       </c>
     </row>
     <row r="17">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.114741935015248</v>
+        <v>0.1147419350152474</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2634654661960728</v>
+        <v>0.263465466196073</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6631920346004125</v>
+        <v>0.6631920346004143</v>
       </c>
     </row>
     <row r="18">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3810056013756248</v>
+        <v>0.3810056013756241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2516542446197337</v>
+        <v>0.2516542446197335</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1300247560438135</v>
+        <v>0.1300247560438138</v>
       </c>
     </row>
     <row r="19">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07577207202969728</v>
+        <v>0.07577207202969674</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2639063601658793</v>
+        <v>0.2639063601658792</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7740225338446046</v>
+        <v>0.7740225338446062</v>
       </c>
     </row>
     <row r="20">
@@ -1881,13 +1881,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1514048112017345</v>
+        <v>0.1514048112017338</v>
       </c>
       <c r="C20" t="n">
-        <v>0.265725401909625</v>
+        <v>0.2657254019096245</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5688274538815595</v>
+        <v>0.5688274538815603</v>
       </c>
     </row>
     <row r="21">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2002496868151333</v>
+        <v>0.2002496868151327</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2549038121769297</v>
+        <v>0.2549038121769295</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4321081823507363</v>
+        <v>0.4321081823507377</v>
       </c>
     </row>
     <row r="22">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.02074852137919063</v>
+        <v>-0.0207485213791909</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2743224548273923</v>
+        <v>0.2743224548273918</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9397090769219663</v>
+        <v>0.9397090769219654</v>
       </c>
     </row>
     <row r="23">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.136848239410876</v>
+        <v>-0.1368482394108766</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2792240338270775</v>
+        <v>0.2792240338270769</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6240617685694625</v>
+        <v>0.6240617685694604</v>
       </c>
     </row>
     <row r="24">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8213945685289853</v>
+        <v>0.8213945685289852</v>
       </c>
       <c r="C24" t="n">
         <v>0.1484879382665879</v>
@@ -1964,10 +1964,10 @@
         <v>-0.6343958972733734</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1108031950759136</v>
+        <v>0.1108031950759137</v>
       </c>
       <c r="D25" t="n">
-        <v>1.031722996890046e-08</v>
+        <v>1.031722996890053e-08</v>
       </c>
     </row>
     <row r="26">
@@ -1980,10 +1980,10 @@
         <v>-0.1361722920117855</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1456889183422689</v>
+        <v>0.145688918342269</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3499540372786659</v>
+        <v>0.349954037278666</v>
       </c>
     </row>
     <row r="27">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.07214589570780622</v>
+        <v>-0.07214589570780633</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1495438291756702</v>
+        <v>0.1495438291756701</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6294935505006781</v>
+        <v>0.6294935505006772</v>
       </c>
     </row>
     <row r="28">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.08070056949942789</v>
+        <v>-0.08070056949942798</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1455600496406537</v>
+        <v>0.1455600496406538</v>
       </c>
       <c r="D28" t="n">
-        <v>0.579295358334623</v>
+        <v>0.5792953583346229</v>
       </c>
     </row>
     <row r="29">
@@ -2025,77 +2025,77 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.267089354671909</v>
+        <v>-0.2670893546719091</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1498065967867202</v>
+        <v>0.1498065967867204</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07460348161737926</v>
+        <v>0.07460348161737959</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.00227667580555176</v>
+        <v>0.01050692349724878</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007061859833278293</v>
+        <v>0.006731266320498107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7471569571762009</v>
+        <v>0.1185441957481897</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01407014842112886</v>
+        <v>0.002276675805551765</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02184983277761062</v>
+        <v>0.007061859833278266</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5196093827488828</v>
+        <v>0.7471569571761995</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01036511117109709</v>
+        <v>0.01407014842112886</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007653933807267214</v>
+        <v>0.02184983277761062</v>
       </c>
       <c r="D32" t="n">
-        <v>0.175666161331694</v>
+        <v>0.5196093827488828</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01050692349724877</v>
+        <v>-0.0103651111710971</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006731266320498111</v>
+        <v>0.007653933807267171</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1185441957481902</v>
+        <v>0.1756661613316913</v>
       </c>
     </row>
   </sheetData>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9076439572638408</v>
+        <v>0.90764395726384</v>
       </c>
       <c r="D3" t="n">
         <v>0.8579106117563428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04973334550749808</v>
+        <v>0.0497333455074972</v>
       </c>
     </row>
     <row r="4">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8958640717713829</v>
+        <v>0.8958640717713821</v>
       </c>
       <c r="D4" t="n">
         <v>0.8263333274535157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06953074431786721</v>
+        <v>0.06953074431786632</v>
       </c>
     </row>
     <row r="5">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8710411710941836</v>
+        <v>0.8710411710941828</v>
       </c>
       <c r="D5" t="n">
         <v>0.794717184639996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07632398645418759</v>
+        <v>0.07632398645418681</v>
       </c>
     </row>
   </sheetData>
@@ -2253,223 +2253,223 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.443505627120429</v>
+        <v>3.443505627120426</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06350082160297775</v>
+        <v>0.06350082160297793</v>
       </c>
       <c r="C2" t="n">
-        <v>3.977080931513962</v>
+        <v>3.977080931513958</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5903149678536181</v>
+        <v>0.590314967853622</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4422973484463544</v>
+        <v>0.4422973484463529</v>
       </c>
       <c r="C3" t="n">
-        <v>1.176911501519803</v>
+        <v>1.176911501519808</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6457416250634053</v>
+        <v>0.6457416250634045</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4216392867904259</v>
+        <v>0.4216392867904264</v>
       </c>
       <c r="C4" t="n">
-        <v>1.245918796657314</v>
+        <v>1.245918796657312</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.115861002202381</v>
+        <v>0.1158610022023802</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7335676596604721</v>
+        <v>0.733567659660473</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4469980577481749</v>
+        <v>0.4469980577481731</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1658506004757244</v>
+        <v>0.1658506004757233</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6838261508744679</v>
+        <v>0.683826150874469</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5482984995282973</v>
+        <v>0.548298499528295</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.05554968572144049</v>
+        <v>0.05554968572144182</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8136733789568202</v>
+        <v>0.813673378956818</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2974783042324357</v>
+        <v>0.2974783042324396</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.342656090985944</v>
+        <v>2.34265609098594</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1258747664385375</v>
+        <v>0.1258747664385384</v>
       </c>
       <c r="C8" t="n">
-        <v>2.989938993583019</v>
+        <v>2.989938993583009</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4191648223707344</v>
+        <v>0.4191648223707343</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5173540760818445</v>
+        <v>0.5173540760818447</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9507760987492939</v>
+        <v>0.9507760987492934</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.563087620801925</v>
+        <v>2.563087620801932</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1093847620548851</v>
+        <v>0.1093847620548842</v>
       </c>
       <c r="C10" t="n">
-        <v>3.192516318722248</v>
+        <v>3.19251631872226</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01850173438861394</v>
+        <v>0.01850173438861364</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8918046158754552</v>
+        <v>0.8918046158754561</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1652004279969323</v>
+        <v>0.1652004279969309</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.7148191238207335</v>
+        <v>0.7148191238207375</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3978486067889285</v>
+        <v>0.3978486067889273</v>
       </c>
       <c r="C12" t="n">
-        <v>1.329708548003158</v>
+        <v>1.329708548003163</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.04867934936202035</v>
+        <v>0.04867934936201988</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8253774474283433</v>
+        <v>0.8253774474283442</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2768740761302473</v>
+        <v>0.2768740761302458</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.182155299407713</v>
+        <v>0.1821552994077127</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6695275158805081</v>
+        <v>0.6695275158805083</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5787847470172088</v>
+        <v>0.5787847470172083</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2993532444747617</v>
+        <v>0.2993532444747614</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5842881627155672</v>
+        <v>0.5842881627155674</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7752480333376608</v>
+        <v>0.7752480333376602</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.04913171654298504</v>
+        <v>0.04913171654298434</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8245810980309505</v>
+        <v>0.8245810980309517</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2782667043496729</v>
+        <v>0.2782667043496708</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.184202881563922</v>
+        <v>1.184202881563915</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2765020303717791</v>
+        <v>0.2765020303717806</v>
       </c>
       <c r="C17" t="n">
-        <v>1.854638020588168</v>
+        <v>1.85463802058816</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.012957618056929</v>
+        <v>1.012957618056925</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3141953264390932</v>
+        <v>0.3141953264390942</v>
       </c>
       <c r="C18" t="n">
-        <v>1.670266373750128</v>
+        <v>1.670266373750124</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.804172748136147</v>
+        <v>2.804172748136167</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09401932927339279</v>
+        <v>0.09401932927339189</v>
       </c>
       <c r="C19" t="n">
-        <v>3.410898801280956</v>
+        <v>3.41089880128097</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.009052018172401106</v>
+        <v>0.009052018172401107</v>
       </c>
       <c r="B20" t="n">
         <v>0.9242019630174032</v>
@@ -2481,49 +2481,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.8613549502279868</v>
+        <v>0.8613549502279859</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3533597960230548</v>
+        <v>0.353359796023055</v>
       </c>
       <c r="C21" t="n">
-        <v>1.500790190192143</v>
+        <v>1.500790190192142</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.3637986136795445</v>
+        <v>0.3637986136795446</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5464041140521181</v>
+        <v>0.5464041140521179</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8719597487040072</v>
+        <v>0.8719597487040078</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.53068688347133</v>
+        <v>1.530686883471329</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2160093850510955</v>
+        <v>0.2160093850510957</v>
       </c>
       <c r="C23" t="n">
-        <v>2.210834099755397</v>
+        <v>2.210834099755396</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.01620963059960668</v>
+        <v>0.01620963059960649</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8986894681032692</v>
+        <v>0.8986894681032698</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1541053998591767</v>
+        <v>0.1541053998591758</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
@@ -2541,58 +2541,58 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.06770591936065652</v>
+        <v>0.06770591936065591</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7947067187302206</v>
+        <v>0.7947067187302215</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3315055533556185</v>
+        <v>0.3315055533556169</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1600402696707893</v>
+        <v>0.1600402696707899</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6891194441918258</v>
+        <v>0.6891194441918254</v>
       </c>
       <c r="C27" t="n">
-        <v>0.537174029797838</v>
+        <v>0.537174029797839</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5.661975765712011</v>
+        <v>5.661975765712024</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01733658270608849</v>
+        <v>0.01733658270608843</v>
       </c>
       <c r="C28" t="n">
-        <v>5.850036639476</v>
+        <v>5.850036639476005</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5185416276853763</v>
+        <v>0.5185416276853744</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4714644459190879</v>
+        <v>0.4714644459190886</v>
       </c>
       <c r="C29" t="n">
-        <v>1.084779116415934</v>
+        <v>1.084779116415932</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.6121910312997706</v>
+        <v>0.6121910312997711</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4339640388345904</v>
+        <v>0.4339640388345903</v>
       </c>
       <c r="C30" t="n">
         <v>1.20435259863361</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.4311172894155775</v>
+        <v>0.4311172894155741</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5114412200502618</v>
+        <v>0.5114412200502634</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9673596543594285</v>
+        <v>0.9673596543594241</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.7749116540198736</v>
+        <v>0.7749116540198746</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3787018686058216</v>
+        <v>0.3787018686058214</v>
       </c>
       <c r="C32" t="n">
         <v>1.400865555044219</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.228476646075272</v>
+        <v>2.228476646075273</v>
       </c>
       <c r="B33" t="n">
         <v>0.1354873718065585</v>
